--- a/evaluation_forms/019_volunteer_attendance_and_reliability_evaluation_form--evaluation_forms.xlsx
+++ b/evaluation_forms/019_volunteer_attendance_and_reliability_evaluation_form--evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -520,7 +520,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>volunteer_attendance_and_reliability_evaluation_form</t>
+          <t>volunteer_form</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -531,7 +531,7 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>date_form</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -554,7 +554,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>volunteer_name</t>
+          <t>volunteer_name_form</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -577,7 +577,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>attendance_score</t>
+          <t>attendance_score_form</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -600,7 +600,7 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,64 +658,64 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>attendance</t>
+          <t>reliability_score_form</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Attendance</t>
+          <t>Reliability</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>reliability_score</t>
+          <t>reliability_score_scale</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Reliability</t>
+          <t>Reliability Score Scale</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>reliability_score_scale</t>
+          <t>reliability_score_scale_value</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Reliability Score Scale</t>
+          <t>Reliability Score Scale Value</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>reliability_score_scale_value</t>
+          <t>comments_form</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Reliability Score Scale Value</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,18 +750,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>email_form</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>phone_form</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>assigned_tool_form</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Assigned Tool</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>assigned_tool_user_form</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Assigned Tool</t>
+          <t>Assigned Tool User</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,246 +842,16 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>assigned_tool_user</t>
+          <t>comments_and_additional_comments</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Assigned Tool User</t>
+          <t>Comments and additional comments</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>comments_and_additional_comments</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Comments and additional comments</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>volunteer_name</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Volunteer Name</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>attendance_score</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Attendance Score</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>attendance_score_scale</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Attendance Score Scale</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>attendance_score_scale_value</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Attendance Score Scale Value</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>attendance</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Attendance</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>reliability_score</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Reliability</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>reliability_score_scale</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Reliability Score Scale</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>reliability_score_scale_value</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Reliability Score Scale Value</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +868,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +901,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'scale_1',_'label':_'scale_1'}</t>
+          <t>scale_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Scale 1', 'label': 'Scale 1'}</t>
+          <t>Scale 1</t>
         </is>
       </c>
     </row>
@@ -1148,12 +918,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'scale_2',_'label':_'scale_2'}</t>
+          <t>scale_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Scale 2', 'label': 'Scale 2'}</t>
+          <t>Scale 2</t>
         </is>
       </c>
     </row>
@@ -1165,12 +935,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'scale_3',_'label':_'scale_3'}</t>
+          <t>scale_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Scale 3', 'label': 'Scale 3'}</t>
+          <t>Scale 3</t>
         </is>
       </c>
     </row>
@@ -1182,12 +952,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'scale_1',_'label':_'scale_1'}</t>
+          <t>scale_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Scale 1', 'label': 'Scale 1'}</t>
+          <t>Scale 1</t>
         </is>
       </c>
     </row>
@@ -1199,12 +969,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'scale_2',_'label':_'scale_2'}</t>
+          <t>scale_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Scale 2', 'label': 'Scale 2'}</t>
+          <t>Scale 2</t>
         </is>
       </c>
     </row>
@@ -1216,114 +986,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'scale_3',_'label':_'scale_3'}</t>
+          <t>scale_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Scale 3', 'label': 'Scale 3'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>attendance_score_scale_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'name':_'scale_1',_'label':_'scale_1'}</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'name': 'Scale 1', 'label': 'Scale 1'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>attendance_score_scale_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'name':_'scale_2',_'label':_'scale_2'}</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'name': 'Scale 2', 'label': 'Scale 2'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>attendance_score_scale_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'name':_'scale_3',_'label':_'scale_3'}</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'name': 'Scale 3', 'label': 'Scale 3'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>reliability_score_scale_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'name':_'scale_1',_'label':_'scale_1'}</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'name': 'Scale 1', 'label': 'Scale 1'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>reliability_score_scale_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'name':_'scale_2',_'label':_'scale_2'}</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'name': 'Scale 2', 'label': 'Scale 2'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>reliability_score_scale_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'name':_'scale_3',_'label':_'scale_3'}</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'name': 'Scale 3', 'label': 'Scale 3'}</t>
+          <t>Scale 3</t>
         </is>
       </c>
     </row>
